--- a/eduservices/SIMULATION_CLASSES.xlsx
+++ b/eduservices/SIMULATION_CLASSES.xlsx
@@ -2278,7 +2278,7 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
     <col hidden="1" width="10" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
@@ -2362,6 +2362,8 @@
       <c r="G9" s="38" t="n"/>
       <c r="H9" s="38" t="n"/>
       <c r="I9" s="38" t="n"/>
+      <c r="J9" s="38" t="n"/>
+      <c r="K9" s="38" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="B10" s="66" t="inlineStr">
@@ -2405,6 +2407,18 @@
         <is>
           <t>Contribution
 ÷ marge complète</t>
+        </is>
+      </c>
+      <c r="J10" s="17" t="inlineStr">
+        <is>
+          <t>Effectif
+par groupe</t>
+        </is>
+      </c>
+      <c r="K10" s="17" t="inlineStr">
+        <is>
+          <t>Point mort
+en élèves</t>
         </is>
       </c>
     </row>
@@ -2441,6 +2455,14 @@
         <f>IF($L11=0,"",IF($H11&lt;=0,"—",$F11/$H11))</f>
         <v/>
       </c>
+      <c r="J11" s="21">
+        <f>IF($L11=0,"",INDEX(Donnees!$AC$1:$AC$400,$L11))</f>
+        <v/>
+      </c>
+      <c r="K11" s="21">
+        <f>IF($L11=0,"",INDEX(Donnees!$AD$1:$AD$400,$L11))</f>
+        <v/>
+      </c>
       <c r="L11" s="9">
         <f>IF(ISERROR(MATCH(Simulation!$AC$4&amp;"#"&amp;1,Donnees!$AB$1:$AB$400,0)),0,MATCH(Simulation!$AC$4&amp;"#"&amp;1,Donnees!$AB$1:$AB$400,0))</f>
         <v/>
@@ -2479,6 +2501,14 @@
         <f>IF($L12=0,"",IF($H12&lt;=0,"—",$F12/$H12))</f>
         <v/>
       </c>
+      <c r="J12" s="21">
+        <f>IF($L12=0,"",INDEX(Donnees!$AC$1:$AC$400,$L12))</f>
+        <v/>
+      </c>
+      <c r="K12" s="21">
+        <f>IF($L12=0,"",INDEX(Donnees!$AD$1:$AD$400,$L12))</f>
+        <v/>
+      </c>
       <c r="L12" s="9">
         <f>IF(ISERROR(MATCH(Simulation!$AC$4&amp;"#"&amp;2,Donnees!$AB$1:$AB$400,0)),0,MATCH(Simulation!$AC$4&amp;"#"&amp;2,Donnees!$AB$1:$AB$400,0))</f>
         <v/>
@@ -2517,6 +2547,14 @@
         <f>IF($L13=0,"",IF($H13&lt;=0,"—",$F13/$H13))</f>
         <v/>
       </c>
+      <c r="J13" s="21">
+        <f>IF($L13=0,"",INDEX(Donnees!$AC$1:$AC$400,$L13))</f>
+        <v/>
+      </c>
+      <c r="K13" s="21">
+        <f>IF($L13=0,"",INDEX(Donnees!$AD$1:$AD$400,$L13))</f>
+        <v/>
+      </c>
       <c r="L13" s="9">
         <f>IF(ISERROR(MATCH(Simulation!$AC$4&amp;"#"&amp;3,Donnees!$AB$1:$AB$400,0)),0,MATCH(Simulation!$AC$4&amp;"#"&amp;3,Donnees!$AB$1:$AB$400,0))</f>
         <v/>
@@ -2555,6 +2593,14 @@
         <f>IF($L14=0,"",IF($H14&lt;=0,"—",$F14/$H14))</f>
         <v/>
       </c>
+      <c r="J14" s="21">
+        <f>IF($L14=0,"",INDEX(Donnees!$AC$1:$AC$400,$L14))</f>
+        <v/>
+      </c>
+      <c r="K14" s="21">
+        <f>IF($L14=0,"",INDEX(Donnees!$AD$1:$AD$400,$L14))</f>
+        <v/>
+      </c>
       <c r="L14" s="9">
         <f>IF(ISERROR(MATCH(Simulation!$AC$4&amp;"#"&amp;4,Donnees!$AB$1:$AB$400,0)),0,MATCH(Simulation!$AC$4&amp;"#"&amp;4,Donnees!$AB$1:$AB$400,0))</f>
         <v/>
@@ -2593,6 +2639,14 @@
         <f>IF($L15=0,"",IF($H15&lt;=0,"—",$F15/$H15))</f>
         <v/>
       </c>
+      <c r="J15" s="21">
+        <f>IF($L15=0,"",INDEX(Donnees!$AC$1:$AC$400,$L15))</f>
+        <v/>
+      </c>
+      <c r="K15" s="21">
+        <f>IF($L15=0,"",INDEX(Donnees!$AD$1:$AD$400,$L15))</f>
+        <v/>
+      </c>
       <c r="L15" s="9">
         <f>IF(ISERROR(MATCH(Simulation!$AC$4&amp;"#"&amp;5,Donnees!$AB$1:$AB$400,0)),0,MATCH(Simulation!$AC$4&amp;"#"&amp;5,Donnees!$AB$1:$AB$400,0))</f>
         <v/>
@@ -2629,6 +2683,8 @@
         <f>IF($H16&lt;=0,"—",$F16/$H16)</f>
         <v/>
       </c>
+      <c r="J16" s="30" t="n"/>
+      <c r="K16" s="30" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="37" t="inlineStr">
@@ -2963,6 +3019,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="K11:K15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>AND($K11&lt;&gt;"",$K11&gt;$J11)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2974,7 +3035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB63"/>
+  <dimension ref="A1:AD63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -3005,6 +3066,8 @@
     <col width="11" customWidth="1" min="26" max="26"/>
     <col width="11" customWidth="1" min="27" max="27"/>
     <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="11" customWidth="1" min="29" max="29"/>
+    <col width="11" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3110,12 +3173,12 @@
           <t>COUT DU PROCHAIN INSCRIT</t>
         </is>
       </c>
-      <c r="T3" s="79" t="inlineStr">
+      <c r="T3" s="78" t="inlineStr">
         <is>
           <t>COUT COMPLET</t>
         </is>
       </c>
-      <c r="U3" s="79" t="inlineStr">
+      <c r="U3" s="78" t="inlineStr">
         <is>
           <t>MARGE COMPLETE</t>
         </is>
@@ -3153,6 +3216,16 @@
       <c r="AB3" s="79" t="inlineStr">
         <is>
           <t>CLE</t>
+        </is>
+      </c>
+      <c r="AC3" s="79" t="inlineStr">
+        <is>
+          <t>EFFECTIF PAR GROUPE</t>
+        </is>
+      </c>
+      <c r="AD3" s="79" t="inlineStr">
+        <is>
+          <t>POINT MORT</t>
         </is>
       </c>
     </row>
@@ -3260,6 +3333,14 @@
         <f>$A4&amp;"#"&amp;$AA4</f>
         <v/>
       </c>
+      <c r="AC4" s="82">
+        <f>J4/G4</f>
+        <v/>
+      </c>
+      <c r="AD4" s="82">
+        <f>(T4/G4)/(V4/J4)</f>
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="80" t="inlineStr">
@@ -3365,6 +3446,14 @@
         <f>$A5&amp;"#"&amp;$AA5</f>
         <v/>
       </c>
+      <c r="AC5" s="82">
+        <f>J5/G5</f>
+        <v/>
+      </c>
+      <c r="AD5" s="82">
+        <f>(T5/G5)/(V5/J5)</f>
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="80" t="inlineStr">
@@ -3470,6 +3559,14 @@
         <f>$A6&amp;"#"&amp;$AA6</f>
         <v/>
       </c>
+      <c r="AC6" s="82">
+        <f>J6/G6</f>
+        <v/>
+      </c>
+      <c r="AD6" s="82">
+        <f>(T6/G6)/(V6/J6)</f>
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="80" t="inlineStr">
@@ -3575,6 +3672,14 @@
         <f>$A7&amp;"#"&amp;$AA7</f>
         <v/>
       </c>
+      <c r="AC7" s="82">
+        <f>J7/G7</f>
+        <v/>
+      </c>
+      <c r="AD7" s="82">
+        <f>(T7/G7)/(V7/J7)</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="80" t="inlineStr">
@@ -3680,6 +3785,14 @@
         <f>$A8&amp;"#"&amp;$AA8</f>
         <v/>
       </c>
+      <c r="AC8" s="82">
+        <f>J8/G8</f>
+        <v/>
+      </c>
+      <c r="AD8" s="82">
+        <f>(T8/G8)/(V8/J8)</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="80" t="inlineStr">
@@ -3785,6 +3898,14 @@
         <f>$A9&amp;"#"&amp;$AA9</f>
         <v/>
       </c>
+      <c r="AC9" s="82">
+        <f>J9/G9</f>
+        <v/>
+      </c>
+      <c r="AD9" s="82">
+        <f>(T9/G9)/(V9/J9)</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="80" t="inlineStr">
@@ -3890,6 +4011,14 @@
         <f>$A10&amp;"#"&amp;$AA10</f>
         <v/>
       </c>
+      <c r="AC10" s="82">
+        <f>J10/G10</f>
+        <v/>
+      </c>
+      <c r="AD10" s="82">
+        <f>(T10/G10)/(V10/J10)</f>
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="80" t="inlineStr">
@@ -3995,6 +4124,14 @@
         <f>$A11&amp;"#"&amp;$AA11</f>
         <v/>
       </c>
+      <c r="AC11" s="82">
+        <f>J11/G11</f>
+        <v/>
+      </c>
+      <c r="AD11" s="82">
+        <f>(T11/G11)/(V11/J11)</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="80" t="inlineStr">
@@ -4100,6 +4237,14 @@
         <f>$A12&amp;"#"&amp;$AA12</f>
         <v/>
       </c>
+      <c r="AC12" s="82">
+        <f>J12/G12</f>
+        <v/>
+      </c>
+      <c r="AD12" s="82">
+        <f>(T12/G12)/(V12/J12)</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="80" t="inlineStr">
@@ -4205,6 +4350,14 @@
         <f>$A13&amp;"#"&amp;$AA13</f>
         <v/>
       </c>
+      <c r="AC13" s="82">
+        <f>J13/G13</f>
+        <v/>
+      </c>
+      <c r="AD13" s="82">
+        <f>(T13/G13)/(V13/J13)</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="80" t="inlineStr">
@@ -4310,6 +4463,14 @@
         <f>$A14&amp;"#"&amp;$AA14</f>
         <v/>
       </c>
+      <c r="AC14" s="82">
+        <f>J14/G14</f>
+        <v/>
+      </c>
+      <c r="AD14" s="82">
+        <f>(T14/G14)/(V14/J14)</f>
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="80" t="inlineStr">
@@ -4415,6 +4576,14 @@
         <f>$A15&amp;"#"&amp;$AA15</f>
         <v/>
       </c>
+      <c r="AC15" s="82">
+        <f>J15/G15</f>
+        <v/>
+      </c>
+      <c r="AD15" s="82">
+        <f>(T15/G15)/(V15/J15)</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="80" t="inlineStr">
@@ -4520,6 +4689,14 @@
         <f>$A16&amp;"#"&amp;$AA16</f>
         <v/>
       </c>
+      <c r="AC16" s="82">
+        <f>J16/G16</f>
+        <v/>
+      </c>
+      <c r="AD16" s="82">
+        <f>(T16/G16)/(V16/J16)</f>
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="80" t="inlineStr">
@@ -4625,6 +4802,14 @@
         <f>$A17&amp;"#"&amp;$AA17</f>
         <v/>
       </c>
+      <c r="AC17" s="82">
+        <f>J17/G17</f>
+        <v/>
+      </c>
+      <c r="AD17" s="82">
+        <f>(T17/G17)/(V17/J17)</f>
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="80" t="inlineStr">
@@ -4730,6 +4915,14 @@
         <f>$A18&amp;"#"&amp;$AA18</f>
         <v/>
       </c>
+      <c r="AC18" s="82">
+        <f>J18/G18</f>
+        <v/>
+      </c>
+      <c r="AD18" s="82">
+        <f>(T18/G18)/(V18/J18)</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="80" t="inlineStr">
@@ -4835,6 +5028,14 @@
         <f>$A19&amp;"#"&amp;$AA19</f>
         <v/>
       </c>
+      <c r="AC19" s="82">
+        <f>J19/G19</f>
+        <v/>
+      </c>
+      <c r="AD19" s="82">
+        <f>(T19/G19)/(V19/J19)</f>
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="80" t="inlineStr">
@@ -4940,6 +5141,14 @@
         <f>$A20&amp;"#"&amp;$AA20</f>
         <v/>
       </c>
+      <c r="AC20" s="82">
+        <f>J20/G20</f>
+        <v/>
+      </c>
+      <c r="AD20" s="82">
+        <f>(T20/G20)/(V20/J20)</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="80" t="inlineStr">
@@ -5045,6 +5254,14 @@
         <f>$A21&amp;"#"&amp;$AA21</f>
         <v/>
       </c>
+      <c r="AC21" s="82">
+        <f>J21/G21</f>
+        <v/>
+      </c>
+      <c r="AD21" s="82">
+        <f>(T21/G21)/(V21/J21)</f>
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="80" t="inlineStr">
@@ -5150,6 +5367,14 @@
         <f>$A22&amp;"#"&amp;$AA22</f>
         <v/>
       </c>
+      <c r="AC22" s="82">
+        <f>J22/G22</f>
+        <v/>
+      </c>
+      <c r="AD22" s="82">
+        <f>(T22/G22)/(V22/J22)</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="80" t="inlineStr">
@@ -5255,6 +5480,14 @@
         <f>$A23&amp;"#"&amp;$AA23</f>
         <v/>
       </c>
+      <c r="AC23" s="82">
+        <f>J23/G23</f>
+        <v/>
+      </c>
+      <c r="AD23" s="82">
+        <f>(T23/G23)/(V23/J23)</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="80" t="inlineStr">
@@ -5360,6 +5593,14 @@
         <f>$A24&amp;"#"&amp;$AA24</f>
         <v/>
       </c>
+      <c r="AC24" s="82">
+        <f>J24/G24</f>
+        <v/>
+      </c>
+      <c r="AD24" s="82">
+        <f>(T24/G24)/(V24/J24)</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="80" t="inlineStr">
@@ -5465,6 +5706,14 @@
         <f>$A25&amp;"#"&amp;$AA25</f>
         <v/>
       </c>
+      <c r="AC25" s="82">
+        <f>J25/G25</f>
+        <v/>
+      </c>
+      <c r="AD25" s="82">
+        <f>(T25/G25)/(V25/J25)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="80" t="inlineStr">
@@ -5570,6 +5819,14 @@
         <f>$A26&amp;"#"&amp;$AA26</f>
         <v/>
       </c>
+      <c r="AC26" s="82">
+        <f>J26/G26</f>
+        <v/>
+      </c>
+      <c r="AD26" s="82">
+        <f>(T26/G26)/(V26/J26)</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="80" t="inlineStr">
@@ -5675,6 +5932,14 @@
         <f>$A27&amp;"#"&amp;$AA27</f>
         <v/>
       </c>
+      <c r="AC27" s="82">
+        <f>J27/G27</f>
+        <v/>
+      </c>
+      <c r="AD27" s="82">
+        <f>(T27/G27)/(V27/J27)</f>
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="80" t="inlineStr">
@@ -5780,6 +6045,14 @@
         <f>$A28&amp;"#"&amp;$AA28</f>
         <v/>
       </c>
+      <c r="AC28" s="82">
+        <f>J28/G28</f>
+        <v/>
+      </c>
+      <c r="AD28" s="82">
+        <f>(T28/G28)/(V28/J28)</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="80" t="inlineStr">
@@ -5885,6 +6158,14 @@
         <f>$A29&amp;"#"&amp;$AA29</f>
         <v/>
       </c>
+      <c r="AC29" s="82">
+        <f>J29/G29</f>
+        <v/>
+      </c>
+      <c r="AD29" s="82">
+        <f>(T29/G29)/(V29/J29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="80" t="inlineStr">
@@ -5990,6 +6271,14 @@
         <f>$A30&amp;"#"&amp;$AA30</f>
         <v/>
       </c>
+      <c r="AC30" s="82">
+        <f>J30/G30</f>
+        <v/>
+      </c>
+      <c r="AD30" s="82">
+        <f>(T30/G30)/(V30/J30)</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="80" t="inlineStr">
@@ -6095,6 +6384,14 @@
         <f>$A31&amp;"#"&amp;$AA31</f>
         <v/>
       </c>
+      <c r="AC31" s="82">
+        <f>J31/G31</f>
+        <v/>
+      </c>
+      <c r="AD31" s="82">
+        <f>(T31/G31)/(V31/J31)</f>
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="80" t="inlineStr">
@@ -6200,6 +6497,14 @@
         <f>$A32&amp;"#"&amp;$AA32</f>
         <v/>
       </c>
+      <c r="AC32" s="82">
+        <f>J32/G32</f>
+        <v/>
+      </c>
+      <c r="AD32" s="82">
+        <f>(T32/G32)/(V32/J32)</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="80" t="inlineStr">
@@ -6305,6 +6610,14 @@
         <f>$A33&amp;"#"&amp;$AA33</f>
         <v/>
       </c>
+      <c r="AC33" s="82">
+        <f>J33/G33</f>
+        <v/>
+      </c>
+      <c r="AD33" s="82">
+        <f>(T33/G33)/(V33/J33)</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="80" t="inlineStr">
@@ -6410,6 +6723,14 @@
         <f>$A34&amp;"#"&amp;$AA34</f>
         <v/>
       </c>
+      <c r="AC34" s="82">
+        <f>J34/G34</f>
+        <v/>
+      </c>
+      <c r="AD34" s="82">
+        <f>(T34/G34)/(V34/J34)</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="80" t="inlineStr">
@@ -6515,6 +6836,14 @@
         <f>$A35&amp;"#"&amp;$AA35</f>
         <v/>
       </c>
+      <c r="AC35" s="82">
+        <f>J35/G35</f>
+        <v/>
+      </c>
+      <c r="AD35" s="82">
+        <f>(T35/G35)/(V35/J35)</f>
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="80" t="inlineStr">
@@ -6620,6 +6949,14 @@
         <f>$A36&amp;"#"&amp;$AA36</f>
         <v/>
       </c>
+      <c r="AC36" s="82">
+        <f>J36/G36</f>
+        <v/>
+      </c>
+      <c r="AD36" s="82">
+        <f>(T36/G36)/(V36/J36)</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="80" t="inlineStr">
@@ -6725,6 +7062,14 @@
         <f>$A37&amp;"#"&amp;$AA37</f>
         <v/>
       </c>
+      <c r="AC37" s="82">
+        <f>J37/G37</f>
+        <v/>
+      </c>
+      <c r="AD37" s="82">
+        <f>(T37/G37)/(V37/J37)</f>
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="80" t="inlineStr">
@@ -6830,6 +7175,14 @@
         <f>$A38&amp;"#"&amp;$AA38</f>
         <v/>
       </c>
+      <c r="AC38" s="82">
+        <f>J38/G38</f>
+        <v/>
+      </c>
+      <c r="AD38" s="82">
+        <f>(T38/G38)/(V38/J38)</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="80" t="inlineStr">
@@ -6935,6 +7288,14 @@
         <f>$A39&amp;"#"&amp;$AA39</f>
         <v/>
       </c>
+      <c r="AC39" s="82">
+        <f>J39/G39</f>
+        <v/>
+      </c>
+      <c r="AD39" s="82">
+        <f>(T39/G39)/(V39/J39)</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="80" t="inlineStr">
@@ -7040,6 +7401,14 @@
         <f>$A40&amp;"#"&amp;$AA40</f>
         <v/>
       </c>
+      <c r="AC40" s="82">
+        <f>J40/G40</f>
+        <v/>
+      </c>
+      <c r="AD40" s="82">
+        <f>(T40/G40)/(V40/J40)</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="80" t="inlineStr">
@@ -7145,6 +7514,14 @@
         <f>$A41&amp;"#"&amp;$AA41</f>
         <v/>
       </c>
+      <c r="AC41" s="82">
+        <f>J41/G41</f>
+        <v/>
+      </c>
+      <c r="AD41" s="82">
+        <f>(T41/G41)/(V41/J41)</f>
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="80" t="inlineStr">
@@ -7250,6 +7627,14 @@
         <f>$A42&amp;"#"&amp;$AA42</f>
         <v/>
       </c>
+      <c r="AC42" s="82">
+        <f>J42/G42</f>
+        <v/>
+      </c>
+      <c r="AD42" s="82">
+        <f>(T42/G42)/(V42/J42)</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="80" t="inlineStr">
@@ -7355,6 +7740,14 @@
         <f>$A43&amp;"#"&amp;$AA43</f>
         <v/>
       </c>
+      <c r="AC43" s="82">
+        <f>J43/G43</f>
+        <v/>
+      </c>
+      <c r="AD43" s="82">
+        <f>(T43/G43)/(V43/J43)</f>
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="80" t="inlineStr">
@@ -7460,6 +7853,14 @@
         <f>$A44&amp;"#"&amp;$AA44</f>
         <v/>
       </c>
+      <c r="AC44" s="82">
+        <f>J44/G44</f>
+        <v/>
+      </c>
+      <c r="AD44" s="82">
+        <f>(T44/G44)/(V44/J44)</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="80" t="inlineStr">
@@ -7565,6 +7966,14 @@
         <f>$A45&amp;"#"&amp;$AA45</f>
         <v/>
       </c>
+      <c r="AC45" s="82">
+        <f>J45/G45</f>
+        <v/>
+      </c>
+      <c r="AD45" s="82">
+        <f>(T45/G45)/(V45/J45)</f>
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="80" t="inlineStr">
@@ -7670,6 +8079,14 @@
         <f>$A46&amp;"#"&amp;$AA46</f>
         <v/>
       </c>
+      <c r="AC46" s="82">
+        <f>J46/G46</f>
+        <v/>
+      </c>
+      <c r="AD46" s="82">
+        <f>(T46/G46)/(V46/J46)</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="80" t="inlineStr">
@@ -7775,6 +8192,14 @@
         <f>$A47&amp;"#"&amp;$AA47</f>
         <v/>
       </c>
+      <c r="AC47" s="82">
+        <f>J47/G47</f>
+        <v/>
+      </c>
+      <c r="AD47" s="82">
+        <f>(T47/G47)/(V47/J47)</f>
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="80" t="inlineStr">
@@ -7880,6 +8305,14 @@
         <f>$A48&amp;"#"&amp;$AA48</f>
         <v/>
       </c>
+      <c r="AC48" s="82">
+        <f>J48/G48</f>
+        <v/>
+      </c>
+      <c r="AD48" s="82">
+        <f>(T48/G48)/(V48/J48)</f>
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="80" t="inlineStr">
@@ -7985,6 +8418,14 @@
         <f>$A49&amp;"#"&amp;$AA49</f>
         <v/>
       </c>
+      <c r="AC49" s="82">
+        <f>J49/G49</f>
+        <v/>
+      </c>
+      <c r="AD49" s="82">
+        <f>(T49/G49)/(V49/J49)</f>
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="80" t="inlineStr">
@@ -8090,6 +8531,14 @@
         <f>$A50&amp;"#"&amp;$AA50</f>
         <v/>
       </c>
+      <c r="AC50" s="82">
+        <f>J50/G50</f>
+        <v/>
+      </c>
+      <c r="AD50" s="82">
+        <f>(T50/G50)/(V50/J50)</f>
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="80" t="inlineStr">
@@ -8195,6 +8644,14 @@
         <f>$A51&amp;"#"&amp;$AA51</f>
         <v/>
       </c>
+      <c r="AC51" s="82">
+        <f>J51/G51</f>
+        <v/>
+      </c>
+      <c r="AD51" s="82">
+        <f>(T51/G51)/(V51/J51)</f>
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="80" t="inlineStr">
@@ -8300,6 +8757,14 @@
         <f>$A52&amp;"#"&amp;$AA52</f>
         <v/>
       </c>
+      <c r="AC52" s="82">
+        <f>J52/G52</f>
+        <v/>
+      </c>
+      <c r="AD52" s="82">
+        <f>(T52/G52)/(V52/J52)</f>
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="80" t="inlineStr">
@@ -8405,6 +8870,14 @@
         <f>$A53&amp;"#"&amp;$AA53</f>
         <v/>
       </c>
+      <c r="AC53" s="82">
+        <f>J53/G53</f>
+        <v/>
+      </c>
+      <c r="AD53" s="82">
+        <f>(T53/G53)/(V53/J53)</f>
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="80" t="inlineStr">
@@ -8510,6 +8983,14 @@
         <f>$A54&amp;"#"&amp;$AA54</f>
         <v/>
       </c>
+      <c r="AC54" s="82">
+        <f>J54/G54</f>
+        <v/>
+      </c>
+      <c r="AD54" s="82">
+        <f>(T54/G54)/(V54/J54)</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="80" t="inlineStr">
@@ -8615,6 +9096,14 @@
         <f>$A55&amp;"#"&amp;$AA55</f>
         <v/>
       </c>
+      <c r="AC55" s="82">
+        <f>J55/G55</f>
+        <v/>
+      </c>
+      <c r="AD55" s="82">
+        <f>(T55/G55)/(V55/J55)</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="80" t="inlineStr">
@@ -8720,6 +9209,14 @@
         <f>$A56&amp;"#"&amp;$AA56</f>
         <v/>
       </c>
+      <c r="AC56" s="82">
+        <f>J56/G56</f>
+        <v/>
+      </c>
+      <c r="AD56" s="82">
+        <f>(T56/G56)/(V56/J56)</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="80" t="inlineStr">
@@ -8825,6 +9322,14 @@
         <f>$A57&amp;"#"&amp;$AA57</f>
         <v/>
       </c>
+      <c r="AC57" s="82">
+        <f>J57/G57</f>
+        <v/>
+      </c>
+      <c r="AD57" s="82">
+        <f>(T57/G57)/(V57/J57)</f>
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="80" t="inlineStr">
@@ -8930,6 +9435,14 @@
         <f>$A58&amp;"#"&amp;$AA58</f>
         <v/>
       </c>
+      <c r="AC58" s="82">
+        <f>J58/G58</f>
+        <v/>
+      </c>
+      <c r="AD58" s="82">
+        <f>(T58/G58)/(V58/J58)</f>
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="80" t="inlineStr">
@@ -9035,6 +9548,14 @@
         <f>$A59&amp;"#"&amp;$AA59</f>
         <v/>
       </c>
+      <c r="AC59" s="82">
+        <f>J59/G59</f>
+        <v/>
+      </c>
+      <c r="AD59" s="82">
+        <f>(T59/G59)/(V59/J59)</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="80" t="inlineStr">
@@ -9140,6 +9661,14 @@
         <f>$A60&amp;"#"&amp;$AA60</f>
         <v/>
       </c>
+      <c r="AC60" s="82">
+        <f>J60/G60</f>
+        <v/>
+      </c>
+      <c r="AD60" s="82">
+        <f>(T60/G60)/(V60/J60)</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="80" t="inlineStr">
@@ -9245,6 +9774,14 @@
         <f>$A61&amp;"#"&amp;$AA61</f>
         <v/>
       </c>
+      <c r="AC61" s="82">
+        <f>J61/G61</f>
+        <v/>
+      </c>
+      <c r="AD61" s="82">
+        <f>(T61/G61)/(V61/J61)</f>
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="80" t="inlineStr">
@@ -9350,6 +9887,14 @@
         <f>$A62&amp;"#"&amp;$AA62</f>
         <v/>
       </c>
+      <c r="AC62" s="82">
+        <f>J62/G62</f>
+        <v/>
+      </c>
+      <c r="AD62" s="82">
+        <f>(T62/G62)/(V62/J62)</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="80" t="inlineStr">
@@ -9453,6 +9998,14 @@
       </c>
       <c r="AB63" s="80">
         <f>$A63&amp;"#"&amp;$AA63</f>
+        <v/>
+      </c>
+      <c r="AC63" s="82">
+        <f>J63/G63</f>
+        <v/>
+      </c>
+      <c r="AD63" s="82">
+        <f>(T63/G63)/(V63/J63)</f>
         <v/>
       </c>
     </row>
